--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065A8E9B-2297-47F1-B6E3-733103A08A58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E251709-E6DA-4635-AFE9-B843AEC988EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -280,6 +280,34 @@
     <t xml:space="preserve">
 Abri a veneziana.</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>messageRussian</t>
+  </si>
+  <si>
+    <t>messageSizeRussian</t>
+  </si>
+  <si>
+    <t>Инвентарь переполнен…</t>
+  </si>
+  <si>
+    <t>Больше этого предмета не унести…</t>
+  </si>
+  <si>
+    <t>Нельзя использовать, пока действует усилитель выносливости.</t>
+  </si>
+  <si>
+    <t>Получен фонарик.
+F или H — включить/выключить свет.</t>
+  </si>
+  <si>
+    <t>Слишком темно, ничего не видно…</t>
+  </si>
+  <si>
+    <t>Трансляция отключена.</t>
+  </si>
+  <si>
+    <t>Рольставня открыта.</t>
   </si>
 </sst>
 </file>
@@ -627,7 +655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" style="1" customWidth="1"/>
@@ -636,10 +664,12 @@
     <col min="5" max="5" width="18.125" customWidth="1"/>
     <col min="6" max="6" width="26.5" customWidth="1"/>
     <col min="7" max="13" width="22.125" customWidth="1"/>
-    <col min="14" max="14" width="9" style="1"/>
+    <col min="14" max="14" width="112.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -679,13 +709,20 @@
       <c r="M1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="N1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" ht="37.5">
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -725,8 +762,14 @@
       <c r="M3">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" ht="37.5">
+      <c r="N3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -766,8 +809,14 @@
       <c r="M4">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" ht="37.5">
+      <c r="N4" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -807,11 +856,17 @@
       <c r="M5">
         <v>22</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" t="s">
+        <v>61</v>
+      </c>
+      <c r="O5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="75">
+    <row r="6" spans="1:16" ht="93.75">
       <c r="A6">
         <v>4</v>
       </c>
@@ -851,8 +906,14 @@
       <c r="M6">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="37.5">
+      <c r="N6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="37.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -892,8 +953,14 @@
       <c r="M7">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="75">
+      <c r="N7" t="s">
+        <v>63</v>
+      </c>
+      <c r="O7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -934,10 +1001,16 @@
         <v>18</v>
       </c>
       <c r="N8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" s="2">
+        <v>18</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="93.75">
+    <row r="9" spans="1:16" ht="93.75">
       <c r="A9">
         <v>7</v>
       </c>
@@ -978,20 +1051,26 @@
         <v>22</v>
       </c>
       <c r="N9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="1">
+        <v>22</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:16">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:16">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:16">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E251709-E6DA-4635-AFE9-B843AEC988EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC088A8-DBBA-474D-8E62-80232208DCF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -308,6 +308,34 @@
   </si>
   <si>
     <t>Рольставня открыта.</t>
+  </si>
+  <si>
+    <t>messageGerman</t>
+  </si>
+  <si>
+    <t>messageSizeGerman</t>
+  </si>
+  <si>
+    <t>Das Inventar ist voll …</t>
+  </si>
+  <si>
+    <t>Von diesem Gegenstand kannst du nicht mehr tragen …</t>
+  </si>
+  <si>
+    <t>Nicht verwendbar, solange der Ausdauer-Booster wirkt.</t>
+  </si>
+  <si>
+    <t>Taschenlampe erhalten.
+F oder H: Licht ein/aus.</t>
+  </si>
+  <si>
+    <t>Es ist zu dunkel, um etwas zu sehen …</t>
+  </si>
+  <si>
+    <t>Die Durchsage wurde abgeschaltet.</t>
+  </si>
+  <si>
+    <t>Der Rollladen ist offen.</t>
   </si>
 </sst>
 </file>
@@ -655,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" style="1" customWidth="1"/>
@@ -666,10 +694,12 @@
     <col min="7" max="13" width="22.125" customWidth="1"/>
     <col min="14" max="14" width="112.625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9" style="1"/>
+    <col min="16" max="16" width="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -715,14 +745,20 @@
       <c r="O1" t="s">
         <v>58</v>
       </c>
+      <c r="P1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:16" ht="37.5">
+    <row r="3" spans="1:18" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -768,8 +804,14 @@
       <c r="O3">
         <v>22</v>
       </c>
+      <c r="P3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q3">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="1:16" ht="37.5">
+    <row r="4" spans="1:18" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -815,8 +857,14 @@
       <c r="O4">
         <v>22</v>
       </c>
+      <c r="P4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" ht="37.5">
+    <row r="5" spans="1:18" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -862,11 +910,17 @@
       <c r="O5">
         <v>22</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q5">
+        <v>22</v>
+      </c>
+      <c r="R5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="93.75">
+    <row r="6" spans="1:18" ht="75">
       <c r="A6">
         <v>4</v>
       </c>
@@ -912,8 +966,14 @@
       <c r="O6">
         <v>22</v>
       </c>
+      <c r="P6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q6">
+        <v>22</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" ht="37.5">
+    <row r="7" spans="1:18" ht="37.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -959,8 +1019,14 @@
       <c r="O7">
         <v>22</v>
       </c>
+      <c r="P7" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q7">
+        <v>22</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" ht="75">
+    <row r="8" spans="1:18" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1007,10 +1073,16 @@
         <v>18</v>
       </c>
       <c r="P8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>18</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="93.75">
+    <row r="9" spans="1:18" ht="93.75">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1057,20 +1129,26 @@
         <v>22</v>
       </c>
       <c r="P9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>22</v>
+      </c>
+      <c r="R9" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC088A8-DBBA-474D-8E62-80232208DCF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6627FA9-F405-4B03-BB9E-122CB8CFC834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="84">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -336,6 +336,34 @@
   </si>
   <si>
     <t>Der Rollladen ist offen.</t>
+  </si>
+  <si>
+    <t>messageFrench</t>
+  </si>
+  <si>
+    <t>messageSizeFrench</t>
+  </si>
+  <si>
+    <t>L'inventaire est plein…</t>
+  </si>
+  <si>
+    <t>Impossible de porter davantage de cet objet…</t>
+  </si>
+  <si>
+    <t>Inutilisable tant que le stimulant d'endurance fait effet.</t>
+  </si>
+  <si>
+    <t>Lampe torche obtenue.
+F ou H : allumer/éteindre.</t>
+  </si>
+  <si>
+    <t>Il fait trop sombre pour y voir…</t>
+  </si>
+  <si>
+    <t>L'annonce a été coupée.</t>
+  </si>
+  <si>
+    <t>Le volet roulant est ouvert.</t>
   </si>
 </sst>
 </file>
@@ -683,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" style="1" customWidth="1"/>
@@ -696,10 +724,12 @@
     <col min="15" max="15" width="20.625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="54" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1"/>
+    <col min="18" max="18" width="52.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -751,14 +781,20 @@
       <c r="Q1" t="s">
         <v>67</v>
       </c>
+      <c r="R1" t="s">
+        <v>75</v>
+      </c>
+      <c r="S1" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:20">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:18" ht="37.5">
+    <row r="3" spans="1:20" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -810,8 +846,14 @@
       <c r="Q3">
         <v>22</v>
       </c>
+      <c r="R3" t="s">
+        <v>77</v>
+      </c>
+      <c r="S3">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="1:18" ht="37.5">
+    <row r="4" spans="1:20" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -863,8 +905,14 @@
       <c r="Q4">
         <v>22</v>
       </c>
+      <c r="R4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S4">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:18" ht="37.5">
+    <row r="5" spans="1:20" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -916,11 +964,17 @@
       <c r="Q5">
         <v>22</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" t="s">
+        <v>79</v>
+      </c>
+      <c r="S5">
+        <v>22</v>
+      </c>
+      <c r="T5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="75">
+    <row r="6" spans="1:20" ht="75">
       <c r="A6">
         <v>4</v>
       </c>
@@ -972,8 +1026,14 @@
       <c r="Q6">
         <v>22</v>
       </c>
+      <c r="R6" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="S6">
+        <v>22</v>
+      </c>
     </row>
-    <row r="7" spans="1:18" ht="37.5">
+    <row r="7" spans="1:20" ht="37.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1025,8 +1085,14 @@
       <c r="Q7">
         <v>22</v>
       </c>
+      <c r="R7" t="s">
+        <v>81</v>
+      </c>
+      <c r="S7">
+        <v>22</v>
+      </c>
     </row>
-    <row r="8" spans="1:18" ht="75">
+    <row r="8" spans="1:20" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1079,10 +1145,16 @@
         <v>18</v>
       </c>
       <c r="R8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="S8" s="2">
+        <v>18</v>
+      </c>
+      <c r="T8" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="93.75">
+    <row r="9" spans="1:20" ht="93.75">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1135,20 +1207,26 @@
         <v>22</v>
       </c>
       <c r="R9" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S9" s="1">
+        <v>22</v>
+      </c>
+      <c r="T9" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:20">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:20">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:20">
       <c r="A12">
         <v>10</v>
       </c>

--- a/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
+++ b/Assets/Originals/Excels/Inventory/InventoryMessage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\001.MyGameProductionBackUp\001.Unity\Mumei\GitFolders\Mumei\Assets\Originals\Excels\Inventory\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6627FA9-F405-4B03-BB9E-122CB8CFC834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924C1FE3-2649-49A2-B7DE-DDF5CAD12DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
   <si>
     <t>number</t>
     <phoneticPr fontId="1"/>
@@ -364,6 +364,34 @@
   </si>
   <si>
     <t>Le volet roulant est ouvert.</t>
+  </si>
+  <si>
+    <t>messageTurkish</t>
+  </si>
+  <si>
+    <t>messageSizeTurkish</t>
+  </si>
+  <si>
+    <t>Envanter dolu…</t>
+  </si>
+  <si>
+    <t>Bu eşyadan daha fazla taşıyamazsın…</t>
+  </si>
+  <si>
+    <t>Dayanıklılık güçlendirici etkinken kullanılamaz.</t>
+  </si>
+  <si>
+    <t>El feneri alındı.
+F veya H: Feneri aç/kapat.</t>
+  </si>
+  <si>
+    <t>Görmek için çok karanlık…</t>
+  </si>
+  <si>
+    <t>Anons sistemi kapatıldı.</t>
+  </si>
+  <si>
+    <t>Kepenk açıldı.</t>
   </si>
 </sst>
 </file>
@@ -711,7 +739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="37.125" style="1" customWidth="1"/>
@@ -726,10 +754,12 @@
     <col min="17" max="17" width="20.375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="52.75" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9" style="1"/>
+    <col min="20" max="20" width="45" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:22">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -787,14 +817,20 @@
       <c r="S1" t="s">
         <v>76</v>
       </c>
+      <c r="T1" t="s">
+        <v>84</v>
+      </c>
+      <c r="U1" t="s">
+        <v>85</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:22">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="37.5">
+    <row r="3" spans="1:22" ht="37.5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -852,8 +888,14 @@
       <c r="S3">
         <v>22</v>
       </c>
+      <c r="T3" t="s">
+        <v>86</v>
+      </c>
+      <c r="U3">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" ht="37.5">
+    <row r="4" spans="1:22" ht="37.5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -911,8 +953,14 @@
       <c r="S4">
         <v>22</v>
       </c>
+      <c r="T4" t="s">
+        <v>87</v>
+      </c>
+      <c r="U4">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="37.5">
+    <row r="5" spans="1:22" ht="37.5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -970,11 +1018,17 @@
       <c r="S5">
         <v>22</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="T5" t="s">
+        <v>88</v>
+      </c>
+      <c r="U5">
+        <v>22</v>
+      </c>
+      <c r="V5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="75">
+    <row r="6" spans="1:22" ht="75">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1032,8 +1086,14 @@
       <c r="S6">
         <v>22</v>
       </c>
+      <c r="T6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="U6">
+        <v>22</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" ht="37.5">
+    <row r="7" spans="1:22" ht="37.5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1091,8 +1151,14 @@
       <c r="S7">
         <v>22</v>
       </c>
+      <c r="T7" t="s">
+        <v>90</v>
+      </c>
+      <c r="U7">
+        <v>22</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" ht="75">
+    <row r="8" spans="1:22" ht="75">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1151,10 +1217,16 @@
         <v>18</v>
       </c>
       <c r="T8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="U8" s="2">
+        <v>18</v>
+      </c>
+      <c r="V8" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="93.75">
+    <row r="9" spans="1:22" ht="93.75">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1213,20 +1285,26 @@
         <v>22</v>
       </c>
       <c r="T9" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="U9" s="1">
+        <v>22</v>
+      </c>
+      <c r="V9" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:22">
       <c r="A10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:22">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:22">
       <c r="A12">
         <v>10</v>
       </c>
